--- a/Student_Data.xlsx
+++ b/Student_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1809076-9CF0-4D98-9211-0E0821A78800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70ACB6F7-0542-4E66-9148-E33C372F7A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0538ABFE-AB6C-4C23-8C82-19551F5CF457}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -162,6 +162,33 @@
   </si>
   <si>
     <t>Monitor</t>
+  </si>
+  <si>
+    <t>Sum =</t>
+  </si>
+  <si>
+    <t>Avg =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IF = </t>
+  </si>
+  <si>
+    <t>Vlookup =</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emp ID </t>
+  </si>
+  <si>
+    <t>Total Sales Ranchi =</t>
+  </si>
+  <si>
+    <t>Ranchi + Laptop ki Sales      =</t>
+  </si>
+  <si>
+    <t>Ranchi + Laptop    =</t>
   </si>
 </sst>
 </file>
@@ -192,7 +219,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -241,6 +268,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -270,7 +327,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -280,9 +337,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -309,6 +363,21 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -316,6 +385,15 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF99CCFF"/>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FFFFFF66"/>
+      <color rgb="FF66FF66"/>
+      <color rgb="FF00FF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -644,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00D6C04-3255-4E37-AB23-69A366051EE1}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -725,7 +803,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="2">
@@ -740,7 +818,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="2">
@@ -755,7 +833,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="2">
@@ -821,13 +899,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -851,7 +929,7 @@
         <v>42</v>
       </c>
       <c r="C22" s="2" t="str">
-        <f t="shared" ref="C22:C24" si="1">IF(B22&gt;=40,"Pass","Fail")</f>
+        <f t="shared" ref="C22:C23" si="1">IF(B22&gt;=40,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
@@ -880,16 +958,16 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
     </row>
@@ -900,7 +978,7 @@
       <c r="B31" s="2">
         <v>450</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <f>B31/500</f>
         <v>0.9</v>
       </c>
@@ -916,7 +994,7 @@
       <c r="B32" s="2">
         <v>380</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <f t="shared" ref="C32:C34" si="2">B32/500</f>
         <v>0.76</v>
       </c>
@@ -932,7 +1010,7 @@
       <c r="B33" s="2">
         <v>290</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <f t="shared" si="2"/>
         <v>0.57999999999999996</v>
       </c>
@@ -948,7 +1026,7 @@
       <c r="B34" s="2">
         <v>495</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="7">
         <f t="shared" si="2"/>
         <v>0.99</v>
       </c>
@@ -958,19 +1036,19 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -981,7 +1059,7 @@
       <c r="B39" s="2">
         <v>55000</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="9">
         <v>0.18</v>
       </c>
       <c r="D39" s="2">
@@ -1000,7 +1078,7 @@
       <c r="B40" s="2">
         <v>500</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="9">
         <v>0.18</v>
       </c>
       <c r="D40" s="2">
@@ -1019,7 +1097,7 @@
       <c r="B41" s="2">
         <v>1200</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="9">
         <v>0.18</v>
       </c>
       <c r="D41" s="2">
@@ -1032,22 +1110,22 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1095,7 +1173,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>104</v>
       </c>
@@ -1106,27 +1184,27 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>501</v>
       </c>
@@ -1147,8 +1225,15 @@
         <f>VLOOKUP(E53,$A$53:$C$56,3,FALSE)</f>
         <v>1500</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I53" t="s">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <f>SUM(C53:C56)</f>
+        <v>58200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>502</v>
       </c>
@@ -1161,8 +1246,15 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I54" t="s">
+        <v>43</v>
+      </c>
+      <c r="J54">
+        <f>AVERAGE(C53:C56)</f>
+        <v>14550</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>503</v>
       </c>
@@ -1172,8 +1264,15 @@
       <c r="C55" s="2">
         <v>1200</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I55" t="s">
+        <v>44</v>
+      </c>
+      <c r="J55" t="str">
+        <f>IF(B21&gt;=40,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>504</v>
       </c>
@@ -1182,6 +1281,377 @@
       </c>
       <c r="C56" s="2">
         <v>1500</v>
+      </c>
+      <c r="I56" t="s">
+        <v>45</v>
+      </c>
+      <c r="J56" t="str">
+        <f>VLOOKUP(A53,$A$53:$C$56,2,FALSE)</f>
+        <v>Laptop</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>101</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="2">
+        <v>30000</v>
+      </c>
+      <c r="E60" s="2">
+        <v>102</v>
+      </c>
+      <c r="F60" s="2" t="str">
+        <f>_xlfn.XLOOKUP(E60,A60:A63,B60:B63)</f>
+        <v>Neha</v>
+      </c>
+      <c r="G60" s="2">
+        <f>_xlfn.XLOOKUP(E60,A60:A63,C60:C63)</f>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>102</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>103</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="2">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>104</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>501</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="2">
+        <v>55000</v>
+      </c>
+      <c r="E67" t="str">
+        <f>INDEX(B67:B70,MATCH(503,A67:A70,0))</f>
+        <v>Keyboard</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>502</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>503</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>504</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="2">
+        <v>10000</v>
+      </c>
+      <c r="D74" t="s">
+        <v>48</v>
+      </c>
+      <c r="F74">
+        <f>SUMIF(A74:A78,"Ranchi",B74:B78)</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="2">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="2">
+        <v>12000</v>
+      </c>
+      <c r="E82" t="s">
+        <v>49</v>
+      </c>
+      <c r="H82">
+        <f>SUMIFS(C82:C86,A82:A86,A82,B82:B86,B82)</f>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90">
+        <f>COUNTIF(A90:A95,"Laptop")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" t="s">
+        <v>50</v>
+      </c>
+      <c r="F99">
+        <f>COUNTIFS(A99:A104,"Ranchi",B99:B104,"Laptop")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
